--- a/product backlog template.xlsx
+++ b/product backlog template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17614\Desktop\Teaching_Assistant_Recruitment_System_Group87\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F5F757D-D55E-4608-8F96-ADBB20E4DA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6DC08-0315-4476-98F0-A5780F28E12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Story ID</t>
   </si>
@@ -55,235 +55,113 @@
     <t>US-01</t>
   </si>
   <si>
-    <t>Create applicant account</t>
-  </si>
-  <si>
-    <t>As a TA applicant,
-I want to create an account on the platform,
-So that I can access vacancies and submit applications online instead of relying on email.</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>1. A TA applicant can register with basic personal details.
-2. The system confirms successful registration.
-3. The applicant can log in with the created account.</t>
-  </si>
-  <si>
     <t>US-02</t>
   </si>
   <si>
-    <t>Maintain reusable applicant profile</t>
-  </si>
-  <si>
-    <t>As a TA applicant,
-I want to save and update my personal information, skills, and CV,
-So that I do not need to fill in the same details every semester.</t>
-  </si>
-  <si>
-    <t>1. The applicant can enter and edit personal information.
-2. The applicant can upload or replace a CV.
-3. Saved profile data can be reused for future applications.</t>
-  </si>
-  <si>
-    <t>Stakeholder: TA | Epic: Applicant profile management | Solves: repetitive and redundant form filling.</t>
-  </si>
-  <si>
     <t>US-03</t>
   </si>
   <si>
-    <t>Browse all TA vacancies</t>
-  </si>
-  <si>
-    <t>As a TA applicant,
-I want to view all available TA vacancies in one place,
-So that I can compare opportunities without searching through separate emails.</t>
-  </si>
-  <si>
-    <t>1. The platform shows a list of all open TA vacancies.
-2. Each vacancy displays the module title and current recruitment status.
-3. Closed or filled vacancies are clearly marked or hidden.</t>
-  </si>
-  <si>
-    <t>Stakeholder: TA | Epic: Vacancy discovery | Solves: applicants cannot centrally view all available posts.</t>
-  </si>
-  <si>
     <t>US-04</t>
   </si>
   <si>
-    <t>View vacancy details</t>
-  </si>
-  <si>
-    <t>As a TA applicant,
-I want to view detailed vacancy information,
-So that I can understand the required skills, working hours, duties, and pay before applying.</t>
-  </si>
-  <si>
-    <t>1. Each vacancy includes module name, number of posts, pay, duties, weekly workload, and required skills.
-2. The applicant can open a details page from the vacancy list.
-3. Information is clearly displayed before application submission.</t>
-  </si>
-  <si>
-    <t>Stakeholder: TA | Epic: Vacancy discovery | Solves: lack of transparency about job requirements.</t>
-  </si>
-  <si>
     <t>US-05</t>
   </si>
   <si>
-    <t>Submit application with skill declaration</t>
-  </si>
-  <si>
-    <t>As a TA applicant,
-I want to apply for a vacancy by selecting the skills I already have and attaching my CV,
-So that the system can assess whether I meet the vacancy requirements.</t>
-  </si>
-  <si>
-    <t>1. The applicant can submit an application for an open vacancy.
-2. The applicant can declare possessed skills from a list.
-3. The system stores the application together with the applicant profile and CV.</t>
-  </si>
-  <si>
-    <t>Stakeholder: TA | Epic: Application submission | Solves: inefficient email submission and unclear skill matching.</t>
-  </si>
-  <si>
-    <t>US-06</t>
-  </si>
-  <si>
-    <t>Track application status</t>
-  </si>
-  <si>
-    <t>As a TA applicant,
-I want to track the status of each application,
-So that I know whether it is submitted, viewed, accepted, rejected, or no longer available.</t>
-  </si>
-  <si>
-    <t>1. The applicant can see all submitted applications on a dashboard.
-2. Each application displays a current status.
-3. Status updates are shown after MO review actions or when a vacancy is filled.</t>
-  </si>
-  <si>
-    <t>Stakeholder: TA | Epic: Application tracking | Solves: applicants cannot know whether they are being considered or whether posts are full.</t>
-  </si>
-  <si>
-    <t>US-07</t>
-  </si>
-  <si>
-    <t>Publish TA vacancies</t>
-  </si>
-  <si>
-    <t>As a Module Organiser (MO),
-I want to create and publish a TA vacancy with clear requirements,
-So that qualified applicants can understand exactly what the role requires.</t>
-  </si>
-  <si>
-    <t>1. The MO can enter module name, number of posts, pay, duties, weekly hours, and required skills.
-2. The vacancy can be published online.
-3. Published vacancies appear to applicants in the vacancy list.</t>
-  </si>
-  <si>
-    <t>Stakeholder: MO | Epic: Vacancy management | Solves: lack of structured vacancy information in email-based recruitment.</t>
-  </si>
-  <si>
-    <t>US-08</t>
-  </si>
-  <si>
-    <t>View applications in one dashboard</t>
-  </si>
-  <si>
-    <t>As a Module Organiser (MO),
-I want to review all applications for a vacancy in one place,
-So that I do not need to read and manage large volumes of recruitment emails manually.</t>
-  </si>
-  <si>
-    <t>1. The MO can open a vacancy and see all related applications in one dashboard.
-2. Each application shows applicant name, submitted CV, and declared skills.
-3. The list is accessible without using external email threads.</t>
-  </si>
-  <si>
-    <t>Stakeholder: MO | Epic: Candidate review | Solves: screening is complex and cumbersome because MOs need to read many emails.</t>
-  </si>
-  <si>
-    <t>US-09</t>
-  </si>
-  <si>
-    <t>Auto-shortlist fully matched applicants</t>
-  </si>
-  <si>
-    <t>As a Module Organiser (MO),
-I want the system to automatically shortlist applicants whose skills fully match the vacancy requirements,
-So that I can identify suitable candidates faster.</t>
-  </si>
-  <si>
-    <t>1. The system compares declared applicant skills with the vacancy requirement list.
-2. Fully matched applicants are shown in the default shortlist.
-3. Non-matching applicants are separated from the default shortlist.</t>
-  </si>
-  <si>
-    <t>Stakeholder: MO | Epic: Candidate filtering | Solves: MOs may not be able to tell whether an applicant meets the skill requirements.</t>
-  </si>
-  <si>
-    <t>US-10</t>
-  </si>
-  <si>
-    <t>Review filtered applicants with missing-skill labels</t>
-  </si>
-  <si>
-    <t>As a Module Organiser (MO),
-I want to view filtered applicants together with the skills they are missing,
-So that I can still consider them when there are not enough fully qualified candidates.</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>1. The MO can access a separate list of filtered applicants.
-2. Missing skills are clearly labelled for each applicant.
-3. The MO can still open the applicant's profile and CV before making a decision.</t>
-  </si>
-  <si>
-    <t>Stakeholder: MO | Epic: Candidate filtering | Solves: flexible review when fully matched applicants are insufficient.</t>
-  </si>
-  <si>
-    <t>US-11</t>
-  </si>
-  <si>
-    <t>Make online hiring decisions</t>
-  </si>
-  <si>
-    <t>As a Module Organiser (MO),
-I want to accept or reject applicants online,
-So that I can complete TA recruitment efficiently and keep applicants informed through the system.</t>
-  </si>
-  <si>
-    <t>1. The MO can mark an application as accepted or rejected.
-2. The applicant status updates immediately after the decision.
-3. Accepted hires reduce the remaining available posts for the vacancy.</t>
-  </si>
-  <si>
-    <t>Stakeholder: MO | Epic: Hiring decision | Solves: inefficient manual communication and delayed status updates.</t>
-  </si>
-  <si>
-    <t>US-12</t>
-  </si>
-  <si>
-    <t>Monitor total TA workload</t>
-  </si>
-  <si>
-    <t>As the system,
-I want to monitor the total allocated workload of each TA across roles,
-So that overloaded applicants can be flagged and intervention can be triggered when necessary.</t>
-  </si>
-  <si>
-    <t>1. The system calculates the total weekly working hours allocated to each TA.
-2. The system flags a TA whose total workload exceeds a defined threshold.
-3. The MO can see the overload warning before finalising allocation.</t>
-  </si>
-  <si>
-    <t>Stakeholder: System/MO | Epic: Allocation control | Solves: risk of overloading TAs across multiple assignments.</t>
-  </si>
-  <si>
-    <t>Stakeholder: TA | Epic: Applicant onboarding | Solves: no fixed recruitment system; scattered email process.</t>
+    <t>Teacher View of TA Skill Matrix</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a course teacher, I want to view a visual skill matrix of all available TAs, so that I can quickly identify TAs with the required skills for my course.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Skill matrix displays TAs with key skills (e.g., programming, grading, lab support)
+2.Skills are color-coded by proficiency level (beginner/intermediate/advanced)
+3.Matrix supports filtering by specific skill requirements
+4.Clicking on a TA shows detailed skill descriptions</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stakeholder: Teacher | Epic: TA Skill Visibility | Solution: Interactive skill matrix UI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Auto-Check TA Course Assignment Limit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> As an administrator, I want the system to automatically check and alert when a TA is assigned to &gt;3 courses, so that I avoid manual resume screening for assignment limits.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.System calculates current course count for each TA in real-time
+2.Red alert appears when assignment count reaches 3 (warning) or 4 (block)
+3.Admin dashboard shows TA assignment status overview
+4.Assignment submission is blocked if it exceeds 3 courses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stakeholder: Administrator | Epic: TA Workload Control | Solution: Rule-based validation engine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Centralized TA Information Dashboard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an administrator, I want a centralized dashboard for all TA-related information, so that I don't have to collect data from multiple sources.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Dashboard integrates TA profiles, course assignments, and performance data
+2.Supports one-click export of TA information reports
+3.Provides real-time updates when TA data changes
+4.Allows filtering and sorting by key parameters (course, skill, status)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stakeholder: Administrator | Epic: TA Data Management | Solution: Unified data visualization platform</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI-Powered TA Resume Initial Screening</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an administrator, I want AI to conduct initial screening of TA resumes against course requirements, so that I reduce manual screening workload.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.AI analyzes resumes for key qualifications (education, experience, skills)
+2.Generates matching scores (0-100) based on course requirements
+3.Flags high-potential candidates (score &gt;80) for priority review
+4.Provides screening reason details for each candidate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stakeholder: Administrator | Epic: AI Recruitment | Solution: NLP-based resume analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Teacher-Friendly TA Application Review</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a course teacher, I want a simplified interface for reviewing TA applications, so that I can efficiently select suitable TAs without technical barriers.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Application cards display key information (skills, experience, availability)
+2.Supports quick rating (1-5 stars) for each applicant
+3.Allows adding short comments for candidate evaluation
+4.Integrates with skill comparison against course requirements</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stakeholder: Teacher | Epic: TA Selection Experience | Solution: User-friendly review interface</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -726,334 +604,222 @@
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="4">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="4">
-        <v>5</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="4">
-        <v>5</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="4">
-        <v>8</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="4">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="4">
-        <v>5</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="4">
-        <v>8</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>

--- a/product backlog template.xlsx
+++ b/product backlog template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17614\Desktop\Teaching_Assistant_Recruitment_System_Group87\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6DC08-0315-4476-98F0-A5780F28E12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F5F757D-D55E-4608-8F96-ADBB20E4DA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
   <si>
     <t>Story ID</t>
   </si>
@@ -55,113 +55,235 @@
     <t>US-01</t>
   </si>
   <si>
+    <t>Create applicant account</t>
+  </si>
+  <si>
+    <t>As a TA applicant,
+I want to create an account on the platform,
+So that I can access vacancies and submit applications online instead of relying on email.</t>
+  </si>
+  <si>
     <t>High</t>
   </si>
   <si>
+    <t>1. A TA applicant can register with basic personal details.
+2. The system confirms successful registration.
+3. The applicant can log in with the created account.</t>
+  </si>
+  <si>
     <t>US-02</t>
   </si>
   <si>
+    <t>Maintain reusable applicant profile</t>
+  </si>
+  <si>
+    <t>As a TA applicant,
+I want to save and update my personal information, skills, and CV,
+So that I do not need to fill in the same details every semester.</t>
+  </si>
+  <si>
+    <t>1. The applicant can enter and edit personal information.
+2. The applicant can upload or replace a CV.
+3. Saved profile data can be reused for future applications.</t>
+  </si>
+  <si>
+    <t>Stakeholder: TA | Epic: Applicant profile management | Solves: repetitive and redundant form filling.</t>
+  </si>
+  <si>
     <t>US-03</t>
   </si>
   <si>
+    <t>Browse all TA vacancies</t>
+  </si>
+  <si>
+    <t>As a TA applicant,
+I want to view all available TA vacancies in one place,
+So that I can compare opportunities without searching through separate emails.</t>
+  </si>
+  <si>
+    <t>1. The platform shows a list of all open TA vacancies.
+2. Each vacancy displays the module title and current recruitment status.
+3. Closed or filled vacancies are clearly marked or hidden.</t>
+  </si>
+  <si>
+    <t>Stakeholder: TA | Epic: Vacancy discovery | Solves: applicants cannot centrally view all available posts.</t>
+  </si>
+  <si>
     <t>US-04</t>
   </si>
   <si>
+    <t>View vacancy details</t>
+  </si>
+  <si>
+    <t>As a TA applicant,
+I want to view detailed vacancy information,
+So that I can understand the required skills, working hours, duties, and pay before applying.</t>
+  </si>
+  <si>
+    <t>1. Each vacancy includes module name, number of posts, pay, duties, weekly workload, and required skills.
+2. The applicant can open a details page from the vacancy list.
+3. Information is clearly displayed before application submission.</t>
+  </si>
+  <si>
+    <t>Stakeholder: TA | Epic: Vacancy discovery | Solves: lack of transparency about job requirements.</t>
+  </si>
+  <si>
     <t>US-05</t>
   </si>
   <si>
-    <t>Teacher View of TA Skill Matrix</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As a course teacher, I want to view a visual skill matrix of all available TAs, so that I can quickly identify TAs with the required skills for my course.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.Skill matrix displays TAs with key skills (e.g., programming, grading, lab support)
-2.Skills are color-coded by proficiency level (beginner/intermediate/advanced)
-3.Matrix supports filtering by specific skill requirements
-4.Clicking on a TA shows detailed skill descriptions</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stakeholder: Teacher | Epic: TA Skill Visibility | Solution: Interactive skill matrix UI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Auto-Check TA Course Assignment Limit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> As an administrator, I want the system to automatically check and alert when a TA is assigned to &gt;3 courses, so that I avoid manual resume screening for assignment limits.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.System calculates current course count for each TA in real-time
-2.Red alert appears when assignment count reaches 3 (warning) or 4 (block)
-3.Admin dashboard shows TA assignment status overview
-4.Assignment submission is blocked if it exceeds 3 courses</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stakeholder: Administrator | Epic: TA Workload Control | Solution: Rule-based validation engine</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Centralized TA Information Dashboard</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As an administrator, I want a centralized dashboard for all TA-related information, so that I don't have to collect data from multiple sources.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.Dashboard integrates TA profiles, course assignments, and performance data
-2.Supports one-click export of TA information reports
-3.Provides real-time updates when TA data changes
-4.Allows filtering and sorting by key parameters (course, skill, status)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Stakeholder: Administrator | Epic: TA Data Management | Solution: Unified data visualization platform</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI-Powered TA Resume Initial Screening</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As an administrator, I want AI to conduct initial screening of TA resumes against course requirements, so that I reduce manual screening workload.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.AI analyzes resumes for key qualifications (education, experience, skills)
-2.Generates matching scores (0-100) based on course requirements
-3.Flags high-potential candidates (score &gt;80) for priority review
-4.Provides screening reason details for each candidate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stakeholder: Administrator | Epic: AI Recruitment | Solution: NLP-based resume analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Teacher-Friendly TA Application Review</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As a course teacher, I want a simplified interface for reviewing TA applications, so that I can efficiently select suitable TAs without technical barriers.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.Application cards display key information (skills, experience, availability)
-2.Supports quick rating (1-5 stars) for each applicant
-3.Allows adding short comments for candidate evaluation
-4.Integrates with skill comparison against course requirements</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stakeholder: Teacher | Epic: TA Selection Experience | Solution: User-friendly review interface</t>
+    <t>Submit application with skill declaration</t>
+  </si>
+  <si>
+    <t>As a TA applicant,
+I want to apply for a vacancy by selecting the skills I already have and attaching my CV,
+So that the system can assess whether I meet the vacancy requirements.</t>
+  </si>
+  <si>
+    <t>1. The applicant can submit an application for an open vacancy.
+2. The applicant can declare possessed skills from a list.
+3. The system stores the application together with the applicant profile and CV.</t>
+  </si>
+  <si>
+    <t>Stakeholder: TA | Epic: Application submission | Solves: inefficient email submission and unclear skill matching.</t>
+  </si>
+  <si>
+    <t>US-06</t>
+  </si>
+  <si>
+    <t>Track application status</t>
+  </si>
+  <si>
+    <t>As a TA applicant,
+I want to track the status of each application,
+So that I know whether it is submitted, viewed, accepted, rejected, or no longer available.</t>
+  </si>
+  <si>
+    <t>1. The applicant can see all submitted applications on a dashboard.
+2. Each application displays a current status.
+3. Status updates are shown after MO review actions or when a vacancy is filled.</t>
+  </si>
+  <si>
+    <t>Stakeholder: TA | Epic: Application tracking | Solves: applicants cannot know whether they are being considered or whether posts are full.</t>
+  </si>
+  <si>
+    <t>US-07</t>
+  </si>
+  <si>
+    <t>Publish TA vacancies</t>
+  </si>
+  <si>
+    <t>As a Module Organiser (MO),
+I want to create and publish a TA vacancy with clear requirements,
+So that qualified applicants can understand exactly what the role requires.</t>
+  </si>
+  <si>
+    <t>1. The MO can enter module name, number of posts, pay, duties, weekly hours, and required skills.
+2. The vacancy can be published online.
+3. Published vacancies appear to applicants in the vacancy list.</t>
+  </si>
+  <si>
+    <t>Stakeholder: MO | Epic: Vacancy management | Solves: lack of structured vacancy information in email-based recruitment.</t>
+  </si>
+  <si>
+    <t>US-08</t>
+  </si>
+  <si>
+    <t>View applications in one dashboard</t>
+  </si>
+  <si>
+    <t>As a Module Organiser (MO),
+I want to review all applications for a vacancy in one place,
+So that I do not need to read and manage large volumes of recruitment emails manually.</t>
+  </si>
+  <si>
+    <t>1. The MO can open a vacancy and see all related applications in one dashboard.
+2. Each application shows applicant name, submitted CV, and declared skills.
+3. The list is accessible without using external email threads.</t>
+  </si>
+  <si>
+    <t>Stakeholder: MO | Epic: Candidate review | Solves: screening is complex and cumbersome because MOs need to read many emails.</t>
+  </si>
+  <si>
+    <t>US-09</t>
+  </si>
+  <si>
+    <t>Auto-shortlist fully matched applicants</t>
+  </si>
+  <si>
+    <t>As a Module Organiser (MO),
+I want the system to automatically shortlist applicants whose skills fully match the vacancy requirements,
+So that I can identify suitable candidates faster.</t>
+  </si>
+  <si>
+    <t>1. The system compares declared applicant skills with the vacancy requirement list.
+2. Fully matched applicants are shown in the default shortlist.
+3. Non-matching applicants are separated from the default shortlist.</t>
+  </si>
+  <si>
+    <t>Stakeholder: MO | Epic: Candidate filtering | Solves: MOs may not be able to tell whether an applicant meets the skill requirements.</t>
+  </si>
+  <si>
+    <t>US-10</t>
+  </si>
+  <si>
+    <t>Review filtered applicants with missing-skill labels</t>
+  </si>
+  <si>
+    <t>As a Module Organiser (MO),
+I want to view filtered applicants together with the skills they are missing,
+So that I can still consider them when there are not enough fully qualified candidates.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>1. The MO can access a separate list of filtered applicants.
+2. Missing skills are clearly labelled for each applicant.
+3. The MO can still open the applicant's profile and CV before making a decision.</t>
+  </si>
+  <si>
+    <t>Stakeholder: MO | Epic: Candidate filtering | Solves: flexible review when fully matched applicants are insufficient.</t>
+  </si>
+  <si>
+    <t>US-11</t>
+  </si>
+  <si>
+    <t>Make online hiring decisions</t>
+  </si>
+  <si>
+    <t>As a Module Organiser (MO),
+I want to accept or reject applicants online,
+So that I can complete TA recruitment efficiently and keep applicants informed through the system.</t>
+  </si>
+  <si>
+    <t>1. The MO can mark an application as accepted or rejected.
+2. The applicant status updates immediately after the decision.
+3. Accepted hires reduce the remaining available posts for the vacancy.</t>
+  </si>
+  <si>
+    <t>Stakeholder: MO | Epic: Hiring decision | Solves: inefficient manual communication and delayed status updates.</t>
+  </si>
+  <si>
+    <t>US-12</t>
+  </si>
+  <si>
+    <t>Monitor total TA workload</t>
+  </si>
+  <si>
+    <t>As the system,
+I want to monitor the total allocated workload of each TA across roles,
+So that overloaded applicants can be flagged and intervention can be triggered when necessary.</t>
+  </si>
+  <si>
+    <t>1. The system calculates the total weekly working hours allocated to each TA.
+2. The system flags a TA whose total workload exceeds a defined threshold.
+3. The MO can see the overload warning before finalising allocation.</t>
+  </si>
+  <si>
+    <t>Stakeholder: System/MO | Epic: Allocation control | Solves: risk of overloading TAs across multiple assignments.</t>
+  </si>
+  <si>
+    <t>Stakeholder: TA | Epic: Applicant onboarding | Solves: no fixed recruitment system; scattered email process.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -604,222 +726,334 @@
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="G5" s="4">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="4">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="G6" s="4">
-        <v>4</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="4">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="4">
+        <v>5</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="4">
+        <v>8</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="4">
+        <v>5</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="4">
+        <v>5</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="4">
+        <v>8</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
